--- a/SmartFactory VLSM.xlsx
+++ b/SmartFactory VLSM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Delta\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Delta\Desktop\Cisco\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCA0090-79D9-4CBC-8138-0F8172E9EA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7766BEBE-CA9C-45B0-8E7C-E42E0CCD4D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7620" yWindow="3450" windowWidth="13725" windowHeight="11835" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11460" yWindow="2940" windowWidth="13725" windowHeight="11835" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla VLSM" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="257">
   <si>
     <t>SmartFactory Colombia S.A.S – Direccionamiento IP con VLSM</t>
   </si>
@@ -797,6 +797,9 @@
   </si>
   <si>
     <t>Access-Point-PT (Access-Point-Admin)</t>
+  </si>
+  <si>
+    <t>Port 0</t>
   </si>
 </sst>
 </file>
@@ -2550,10 +2553,10 @@
         <v>255</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>183</v>
+        <v>256</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>168</v>
@@ -2573,7 +2576,7 @@
         <v>166</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>168</v>

--- a/SmartFactory VLSM.xlsx
+++ b/SmartFactory VLSM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Delta\Desktop\Cisco\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7766BEBE-CA9C-45B0-8E7C-E42E0CCD4D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23B6E28-1A20-465B-A3FD-1A431B6CB390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11460" yWindow="2940" windowWidth="13725" windowHeight="11835" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="258">
   <si>
     <t>SmartFactory Colombia S.A.S – Direccionamiento IP con VLSM</t>
   </si>
@@ -580,9 +580,6 @@
     <t>fa0/7</t>
   </si>
   <si>
-    <t>0/1</t>
-  </si>
-  <si>
     <t>fa0/8</t>
   </si>
   <si>
@@ -800,6 +797,12 @@
   </si>
   <si>
     <t>Port 0</t>
+  </si>
+  <si>
+    <t>0/0</t>
+  </si>
+  <si>
+    <t>Telefono-IoT</t>
   </si>
 </sst>
 </file>
@@ -2358,7 +2361,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -2550,13 +2553,13 @@
     </row>
     <row r="12" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>256</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>168</v>
@@ -2570,13 +2573,13 @@
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>166</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>168</v>
@@ -2590,7 +2593,7 @@
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B14" s="33"/>
       <c r="C14" s="33"/>
@@ -2600,7 +2603,7 @@
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>166</v>
@@ -2609,10 +2612,10 @@
         <v>167</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>170</v>
@@ -2620,7 +2623,7 @@
     </row>
     <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>166</v>
@@ -2629,10 +2632,10 @@
         <v>172</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>170</v>
@@ -2640,7 +2643,7 @@
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>166</v>
@@ -2649,10 +2652,10 @@
         <v>174</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>170</v>
@@ -2660,7 +2663,7 @@
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>166</v>
@@ -2669,10 +2672,10 @@
         <v>176</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>170</v>
@@ -2680,7 +2683,7 @@
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>166</v>
@@ -2689,10 +2692,10 @@
         <v>178</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>170</v>
@@ -2700,7 +2703,7 @@
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>166</v>
@@ -2709,10 +2712,10 @@
         <v>180</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>170</v>
@@ -2720,7 +2723,7 @@
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>166</v>
@@ -2729,10 +2732,10 @@
         <v>182</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>170</v>
@@ -2740,7 +2743,7 @@
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="38" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B22" s="33"/>
       <c r="C22" s="33"/>
@@ -2759,7 +2762,7 @@
         <v>167</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>108</v>
@@ -2773,13 +2776,13 @@
         <v>106</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>200</v>
-      </c>
       <c r="D24" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>108</v>
@@ -2799,7 +2802,7 @@
         <v>172</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>108</v>
@@ -2810,7 +2813,7 @@
     </row>
     <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
@@ -2820,13 +2823,13 @@
     </row>
     <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>203</v>
-      </c>
       <c r="C27" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>123</v>
@@ -2840,13 +2843,13 @@
     </row>
     <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>123</v>
@@ -2860,13 +2863,13 @@
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>123</v>
@@ -2880,13 +2883,13 @@
     </row>
     <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>123</v>
@@ -2900,66 +2903,66 @@
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="C31" s="12" t="s">
+      <c r="E31" s="12">
+        <v>40</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D32" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="E31" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-    </row>
-    <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>170</v>
-      </c>
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
     </row>
     <row r="34" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="23" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>166</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>132</v>
@@ -2970,56 +2973,56 @@
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>166</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>132</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>212</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="23" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>132</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="23" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>132</v>
@@ -3030,16 +3033,16 @@
     </row>
     <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="23" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>132</v>
@@ -3049,47 +3052,47 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
+      <c r="A39" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>170</v>
-      </c>
+      <c r="A40" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="B40" s="33"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B41" s="18" t="s">
         <v>166</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E41" s="18" t="s">
         <v>86</v>
@@ -3100,16 +3103,16 @@
     </row>
     <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="20" t="s">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>221</v>
+        <v>166</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E42" s="18" t="s">
         <v>86</v>
@@ -3120,16 +3123,16 @@
     </row>
     <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B43" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="C43" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="C43" s="18" t="s">
-        <v>223</v>
-      </c>
       <c r="D43" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>86</v>
@@ -3140,16 +3143,16 @@
     </row>
     <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="20" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>86</v>
@@ -3160,16 +3163,16 @@
     </row>
     <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E45" s="18" t="s">
         <v>86</v>
@@ -3179,44 +3182,44 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="B46" s="33"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
+      <c r="A46" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="B47" s="30" t="s">
-        <v>227</v>
-      </c>
-      <c r="C47" s="30" t="s">
-        <v>228</v>
-      </c>
-      <c r="D47" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="E47" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="F47" s="31" t="s">
-        <v>229</v>
-      </c>
+      <c r="A47" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
     </row>
     <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="B48" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="C48" s="30" t="s">
         <v>227</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>230</v>
       </c>
       <c r="D48" s="31" t="s">
         <v>143</v>
@@ -3225,18 +3228,18 @@
         <v>139</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="29" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D49" s="31" t="s">
         <v>143</v>
@@ -3245,18 +3248,18 @@
         <v>139</v>
       </c>
       <c r="F49" s="31" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B50" s="30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C50" s="30" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D50" s="31" t="s">
         <v>143</v>
@@ -3265,18 +3268,18 @@
         <v>139</v>
       </c>
       <c r="F50" s="31" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="29" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B51" s="30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D51" s="31" t="s">
         <v>143</v>
@@ -3285,18 +3288,18 @@
         <v>139</v>
       </c>
       <c r="F51" s="31" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B52" s="30" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="C52" s="30" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D52" s="31" t="s">
         <v>143</v>
@@ -3305,41 +3308,41 @@
         <v>139</v>
       </c>
       <c r="F52" s="31" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" s="31" t="s">
         <v>143</v>
-      </c>
-      <c r="B53" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>227</v>
-      </c>
-      <c r="D53" s="31" t="s">
-        <v>137</v>
       </c>
       <c r="E53" s="30" t="s">
         <v>139</v>
       </c>
       <c r="F53" s="31" t="s">
-        <v>170</v>
+        <v>238</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="B54" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="D54" s="31" t="s">
         <v>137</v>
-      </c>
-      <c r="B54" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="D54" s="31" t="s">
-        <v>243</v>
       </c>
       <c r="E54" s="30" t="s">
         <v>139</v>
@@ -3350,16 +3353,16 @@
     </row>
     <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="29" t="s">
-        <v>243</v>
+        <v>137</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C55" s="30" t="s">
         <v>241</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="E55" s="30" t="s">
         <v>139</v>
@@ -3370,85 +3373,105 @@
     </row>
     <row r="56" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="B56" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="D56" s="31" t="s">
         <v>153</v>
-      </c>
-      <c r="B56" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="C56" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="D56" s="31" t="s">
-        <v>247</v>
       </c>
       <c r="E56" s="30" t="s">
         <v>139</v>
       </c>
       <c r="F56" s="31" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B57" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="D57" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="E57" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="F57" s="31" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="32" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="B57" s="33"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="33"/>
-      <c r="F57" s="33"/>
-    </row>
-    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="B58" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="C58" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="D58" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="E58" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="F58" s="31" t="s">
-        <v>251</v>
-      </c>
+      <c r="B58" s="33"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="33"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="33"/>
     </row>
     <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="29" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>246</v>
+        <v>202</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="D59" s="31" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="E59" s="30" t="s">
         <v>139</v>
       </c>
       <c r="F59" s="31" t="s">
-        <v>252</v>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="D60" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="E60" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="F60" s="31" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A40:F40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SmartFactory VLSM.xlsx
+++ b/SmartFactory VLSM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Delta\Desktop\Cisco\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23B6E28-1A20-465B-A3FD-1A431B6CB390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1762D992-2B42-4245-AF1A-7B25A8D52B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11460" yWindow="2940" windowWidth="13725" windowHeight="11835" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7455" yWindow="1860" windowWidth="13725" windowHeight="11835" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla VLSM" sheetId="1" r:id="rId1"/>
@@ -781,9 +781,6 @@
     <t>Laptop-PT (Cliente VPN)</t>
   </si>
   <si>
-    <t>NO conectado (cliente VPN externo)</t>
-  </si>
-  <si>
     <t>NO (nube Internet simulada)</t>
   </si>
   <si>
@@ -803,6 +800,9 @@
   </si>
   <si>
     <t>Telefono-IoT</t>
+  </si>
+  <si>
+    <t>Conectado (Simulacion de Cliente VPN)</t>
   </si>
 </sst>
 </file>
@@ -2553,10 +2553,10 @@
     </row>
     <row r="12" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>185</v>
@@ -2903,7 +2903,7 @@
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>202</v>
@@ -2926,7 +2926,7 @@
         <v>123</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>167</v>
@@ -3109,7 +3109,7 @@
         <v>166</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>218</v>
@@ -3316,7 +3316,7 @@
         <v>218</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C53" s="30" t="s">
         <v>237</v>
@@ -3426,19 +3426,19 @@
         <v>249</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="D59" s="31" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E59" s="30" t="s">
         <v>139</v>
       </c>
       <c r="F59" s="31" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3458,7 +3458,7 @@
         <v>139</v>
       </c>
       <c r="F60" s="31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
